--- a/data/trending_integrated_20261008_12.xlsx
+++ b/data/trending_integrated_20261008_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30837018000</v>
+        <v>30861071720</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14110</v>
+        <v>14060</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.68%</t>
+          <t>'+17.26%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>40395488030</v>
+        <v>40714674685</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11330</v>
+        <v>11290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.68%</t>
+          <t>'+14.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>50848094355</v>
+        <v>51376807035</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38700</v>
+        <v>13450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.91%</t>
+          <t>'+7.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H5" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K5" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L5" t="n">
-        <v>39850</v>
+        <v>14200</v>
       </c>
       <c r="M5" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N5" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>106805120475</v>
+        <v>76813148755</v>
       </c>
       <c r="P5" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q5" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R5" t="n">
-        <v>199000</v>
+        <v>-324000</v>
       </c>
       <c r="S5" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>JP모건 등 기관/외인 매수세 유입, 추세 긍정적 평가 및 4만원 안착 기대.</t>
+          <t>유증 물량 정리 후 주가 상승 기대감, 바이오스텝 및 HLB 승인 관련 논의.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['기관/외인', '매수세', '추세']</t>
+          <t>['유증 물량', '바이오스텝', 'HLB 승인']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6900</v>
+        <v>38475</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.81%</t>
+          <t>'+6.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>31.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6460</v>
+        <v>36200</v>
       </c>
       <c r="K6" t="n">
-        <v>6930</v>
+        <v>36250</v>
       </c>
       <c r="L6" t="n">
-        <v>8390</v>
+        <v>39850</v>
       </c>
       <c r="M6" t="n">
-        <v>6730</v>
+        <v>36000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.31</v>
+        <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>19661531320</v>
+        <v>107930775300</v>
       </c>
       <c r="P6" t="n">
-        <v>9680</v>
+        <v>45000</v>
       </c>
       <c r="Q6" t="n">
-        <v>371</v>
+        <v>15530</v>
       </c>
       <c r="R6" t="n">
-        <v>-25000</v>
+        <v>199000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
+          <t>JP모건 등 기관 및 외국인의 매수세 유입. 긍정적 추세 확인 및 실적 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['관리종목', '해제', '호재']</t>
+          <t>['기관 매수', '추세', '실적']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13360</v>
+        <v>6850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.28%</t>
+          <t>'+6.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12570</v>
+        <v>6460</v>
       </c>
       <c r="K7" t="n">
-        <v>12970</v>
+        <v>6930</v>
       </c>
       <c r="L7" t="n">
-        <v>14200</v>
+        <v>8390</v>
       </c>
       <c r="M7" t="n">
-        <v>12500</v>
+        <v>6730</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>0.31</v>
       </c>
       <c r="O7" t="n">
-        <v>75862269930</v>
+        <v>19859712660</v>
       </c>
       <c r="P7" t="n">
-        <v>22250</v>
+        <v>9680</v>
       </c>
       <c r="Q7" t="n">
-        <v>6000</v>
+        <v>371</v>
       </c>
       <c r="R7" t="n">
-        <v>-324000</v>
+        <v>-25000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유증 물량 정리 후 주가 상승 기대감, 바이오스텝 및 HLB 승인 관련 논의.</t>
+          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유증 물량', '바이오스텝', 'HLB 승인']</t>
+          <t>['관리종목', '해제', '호재']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1739000</v>
+        <v>1731000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.93%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G8" t="n">
-        <v>1410</v>
+        <v>1379</v>
       </c>
       <c r="H8" t="n">
         <v>49.59</v>
@@ -1162,7 +1162,7 @@
         <v>49.71</v>
       </c>
       <c r="O8" t="n">
-        <v>2219877233000</v>
+        <v>2294277141500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 상장 이슈 관련 언급. 자사주 매입 및 외인 매매 동향 주시. 일부 긍정적 기대감.</t>
+          <t>솔리다임 상장 관련 논란으로 인한 주주 불만. 정부의 정책 비판.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '자사주 매입', '외인 동향']</t>
+          <t>['솔리다임', '상장', '주주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4450</v>
+        <v>45925</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.05%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.19</v>
+        <v>-0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="G9" t="n">
-        <v>149</v>
+        <v>942</v>
       </c>
       <c r="H9" t="n">
-        <v>4.46</v>
+        <v>13.39</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4430</v>
+        <v>45900</v>
       </c>
       <c r="K9" t="n">
-        <v>4650</v>
+        <v>45950</v>
       </c>
       <c r="L9" t="n">
-        <v>4855</v>
+        <v>46500</v>
       </c>
       <c r="M9" t="n">
-        <v>4185</v>
+        <v>45100</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>14.12</v>
       </c>
       <c r="O9" t="n">
-        <v>80825567849</v>
+        <v>26999924875</v>
       </c>
       <c r="P9" t="n">
-        <v>5470</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>2810</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-469000</v>
+        <v>-12000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국제약품, 미국 항생제 회사 주가 폭등 및 WHO 관련 뉴스에 대한 기대감. 하지만 구체적인 사업 연관성이나 팩트 기반 분석은 부족.</t>
+          <t>HLB 리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 긍정적 주가 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['항생제', 'WHO', '주가']</t>
+          <t>['리보세라닙', '허가', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,130 +1292,130 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45900</v>
+        <v>8220</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.36%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>250</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>911</v>
+        <v>191</v>
       </c>
       <c r="H10" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K10" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L10" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M10" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N10" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>26540289800</v>
+        <v>11931504690</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-6000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB, 리보세라닙 병용요법 허가 기대감 속에서 공매도와의 관계 언급. 긍정적 차트 분석 및 우상향 전망.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '우상향']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8250</v>
+        <v>4385</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>1.19</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="H11" t="n">
-        <v>26.38</v>
+        <v>4.46</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,60 +1423,60 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8250</v>
+        <v>4430</v>
       </c>
       <c r="K11" t="n">
-        <v>8190</v>
+        <v>4650</v>
       </c>
       <c r="L11" t="n">
-        <v>8320</v>
+        <v>4855</v>
       </c>
       <c r="M11" t="n">
-        <v>8090</v>
+        <v>4185</v>
       </c>
       <c r="N11" t="n">
-        <v>26.55</v>
+        <v>3.27</v>
       </c>
       <c r="O11" t="n">
-        <v>11554564925</v>
+        <v>81743402889</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>5470</v>
       </c>
       <c r="Q11" t="n">
-        <v>8090</v>
+        <v>2810</v>
       </c>
       <c r="R11" t="n">
-        <v>-6000</v>
+        <v>-469000</v>
       </c>
       <c r="S11" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 전염병 관련 불확실성 언급. 국제 분위기상 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['항생제', 'WHO', '전염병']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>266250</v>
+        <v>265500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="G12" t="n">
-        <v>1748</v>
+        <v>1713</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>2255879183250</v>
+        <v>2321763836500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>107조 영업이익에도 주가 부양 실패, 정치적 요인 및 외인/기관 행태에 대한 불만 제기.</t>
+          <t>삼성전자 107조 분기 영업이익에도 불구하고 주가 부양되지 않는 현실에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '외인/기관']</t>
+          <t>['영업이익', '주가 부양', '실적']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16840</v>
+        <v>16850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.88%</t>
+          <t>'-2.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="H13" t="n">
         <v>9.460000000000001</v>
@@ -1622,7 +1622,7 @@
         <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>28615421500</v>
+        <v>29404525430</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18930</v>
+        <v>18925</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>32555469540</v>
+        <v>33239404355</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>증권사 애널리스트 불신, 주가 하락 및 폐업 우려, 조선주 전반에 대한 부정적 전망.</t>
+          <t>증권사 애널리스트 및 방송, 유튜브, 리딩방의 투자 조언에 대한 불신. 조선주 전반의 부진.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['증권사 애널리스트', '주가 하락', '조선주']</t>
+          <t>['애널리스트', '조선주', '투자']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,79 +1759,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28500</v>
+        <v>232000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-3.73%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.76</v>
+        <v>-0.65</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="G15" t="n">
-        <v>136</v>
+        <v>666</v>
       </c>
       <c r="H15" t="n">
-        <v>10.02</v>
+        <v>3.47</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29800</v>
+        <v>241000</v>
       </c>
       <c r="K15" t="n">
-        <v>29900</v>
+        <v>227000</v>
       </c>
       <c r="L15" t="n">
-        <v>30000</v>
+        <v>239500</v>
       </c>
       <c r="M15" t="n">
-        <v>28400</v>
+        <v>210500</v>
       </c>
       <c r="N15" t="n">
-        <v>10.78</v>
+        <v>4.12</v>
       </c>
       <c r="O15" t="n">
-        <v>45396286400</v>
+        <v>36216746750</v>
       </c>
       <c r="P15" t="n">
-        <v>75900</v>
+        <v>1233000</v>
       </c>
       <c r="Q15" t="n">
-        <v>15960</v>
+        <v>120000</v>
       </c>
       <c r="R15" t="n">
-        <v>-380000</v>
+        <v>5000</v>
       </c>
       <c r="S15" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>삼천당제약, 아일리아 영업이익 전망 및 연기금 매수 동향. 릴레이 계약공시 및 공매도 금지 관련 긍정적 뉴스.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['아일리아', '연기금', '계약공시']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,43 +1839,43 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>230500</v>
+        <v>13160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-4.57%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.65</v>
+        <v>-0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="G16" t="n">
-        <v>656</v>
+        <v>887</v>
       </c>
       <c r="H16" t="n">
-        <v>3.47</v>
+        <v>0.09</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>241000</v>
+        <v>13790</v>
       </c>
       <c r="K16" t="n">
-        <v>227000</v>
+        <v>13410</v>
       </c>
       <c r="L16" t="n">
-        <v>239500</v>
+        <v>13940</v>
       </c>
       <c r="M16" t="n">
-        <v>210500</v>
+        <v>11600</v>
       </c>
       <c r="N16" t="n">
-        <v>4.12</v>
+        <v>0.24</v>
       </c>
       <c r="O16" t="n">
-        <v>35669964250</v>
+        <v>37436068820</v>
       </c>
       <c r="P16" t="n">
-        <v>1233000</v>
+        <v>28700</v>
       </c>
       <c r="Q16" t="n">
-        <v>120000</v>
+        <v>11600</v>
       </c>
       <c r="R16" t="n">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼천당제약, 아일리아 영업이익 전망 및 연기금 매수 동향. 릴레이 계약공시 및 공매도 금지 관련 긍정적 뉴스.</t>
+          <t>덕산넵코어스의 사기 상장 의혹 및 중복 상장 예외 허용에 대한 비판. 금융당국 및 정부 불신.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['아일리아', '연기금', '계약공시']</t>
+          <t>['사기 상장', '중복 상장', '금융당국']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,99 +1936,99 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16940</v>
+        <v>28400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.57%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>435</v>
+        <v>142</v>
       </c>
       <c r="H17" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17940</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
-        <v>17770</v>
+        <v>29900</v>
       </c>
       <c r="L17" t="n">
-        <v>17940</v>
+        <v>30000</v>
       </c>
       <c r="M17" t="n">
-        <v>16800</v>
+        <v>28400</v>
       </c>
       <c r="N17" t="n">
-        <v>4.92</v>
+        <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>77968900860</v>
+        <v>47072411200</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>-168000</v>
+        <v>-380000</v>
       </c>
       <c r="S17" t="n">
-        <v>-15000</v>
+        <v>6000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 급락 영향 우려, 외인 매수세와 프로그램 매매에 대한 불신.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신주', '미국 증시', '외인 매매']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7360</v>
+        <v>7390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-5.50%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-2.03</v>
       </c>
       <c r="E18" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="H18" t="n">
         <v>3.09</v>
@@ -2082,7 +2082,7 @@
         <v>5.12</v>
       </c>
       <c r="O18" t="n">
-        <v>78750641325</v>
+        <v>79769156930</v>
       </c>
       <c r="P18" t="n">
         <v>23500</v>
@@ -2127,83 +2127,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75700</v>
+        <v>16920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.96%</t>
+          <t>'-5.69%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.95</v>
       </c>
       <c r="E19" t="n">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="F19" t="n">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="G19" t="n">
-        <v>912</v>
+        <v>442</v>
       </c>
       <c r="H19" t="n">
-        <v>22.49</v>
+        <v>3.97</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>80500</v>
+        <v>17940</v>
       </c>
       <c r="K19" t="n">
-        <v>79600</v>
+        <v>17770</v>
       </c>
       <c r="L19" t="n">
-        <v>79600</v>
+        <v>17940</v>
       </c>
       <c r="M19" t="n">
-        <v>75600</v>
+        <v>16800</v>
       </c>
       <c r="N19" t="n">
-        <v>22.59</v>
+        <v>4.92</v>
       </c>
       <c r="O19" t="n">
-        <v>156375920150</v>
+        <v>78856961130</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-360000</v>
+        <v>-168000</v>
       </c>
       <c r="S19" t="n">
-        <v>-54000</v>
+        <v>-15000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 한미 텍사스 가스발전 확정 및 원전 관련 뉴스 언급. 하지만 주가 하락에 대한 불만과 공매도 관련 언급.</t>
+          <t>미국 광통신 주가 하락에 따른 대한광통신 주가 변동성에 대한 우려. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['광통신', '주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4880</v>
+        <v>75700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.33%</t>
+          <t>'-5.96%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>336</v>
       </c>
       <c r="F20" t="n">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>302</v>
+        <v>947</v>
       </c>
       <c r="H20" t="n">
-        <v>4.65</v>
+        <v>22.49</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5210</v>
+        <v>80500</v>
       </c>
       <c r="K20" t="n">
-        <v>5220</v>
+        <v>79600</v>
       </c>
       <c r="L20" t="n">
-        <v>5310</v>
+        <v>79600</v>
       </c>
       <c r="M20" t="n">
-        <v>4755</v>
+        <v>75600</v>
       </c>
       <c r="N20" t="n">
-        <v>4.72</v>
+        <v>22.59</v>
       </c>
       <c r="O20" t="n">
-        <v>61539003169</v>
+        <v>161725188150</v>
       </c>
       <c r="P20" t="n">
-        <v>8100</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>592</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-152000</v>
+        <v>-360000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-54000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 대량 매도 우려, 주가 급등 기대와 단기 매도세 혼재.</t>
+          <t>두산에너빌리티, 한미 텍사스 가스발전 확정 및 원전 관련 뉴스 언급. 하지만 주가 하락에 대한 불만과 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['전환사채', '대량 매도', '주가 전망']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>54000</v>
+        <v>4865</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.06%</t>
+          <t>'-6.62%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>274</v>
+        <v>90</v>
       </c>
       <c r="F21" t="n">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>531</v>
+        <v>302</v>
       </c>
       <c r="H21" t="n">
-        <v>1.32</v>
+        <v>4.65</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>58100</v>
+        <v>5210</v>
       </c>
       <c r="K21" t="n">
-        <v>63200</v>
+        <v>5220</v>
       </c>
       <c r="L21" t="n">
-        <v>63800</v>
+        <v>5310</v>
       </c>
       <c r="M21" t="n">
-        <v>53100</v>
+        <v>4755</v>
       </c>
       <c r="N21" t="n">
-        <v>1.3</v>
+        <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>48891693100</v>
+        <v>61994164177</v>
       </c>
       <c r="P21" t="n">
-        <v>63800</v>
+        <v>8100</v>
       </c>
       <c r="Q21" t="n">
-        <v>25600</v>
+        <v>592</v>
       </c>
       <c r="R21" t="n">
-        <v>-170000</v>
+        <v>-152000</v>
       </c>
       <c r="S21" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 조작 신고 및 차명 거래 의혹 제기, 공매도에 대한 부정적 시각.</t>
+          <t>전환사채 발행 및 대량 매도 우려, 주가 급등 기대와 단기 매도세 혼재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '차명 거래']</t>
+          <t>['전환사채', '대량 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9910</v>
+        <v>53600</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.99%</t>
+          <t>'-7.75%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>280</v>
       </c>
       <c r="F22" t="n">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="G22" t="n">
-        <v>336</v>
+        <v>533</v>
       </c>
       <c r="H22" t="n">
-        <v>5.04</v>
+        <v>1.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>11010</v>
+        <v>58100</v>
       </c>
       <c r="K22" t="n">
-        <v>10110</v>
+        <v>63200</v>
       </c>
       <c r="L22" t="n">
-        <v>10130</v>
+        <v>63800</v>
       </c>
       <c r="M22" t="n">
-        <v>9750</v>
+        <v>53100</v>
       </c>
       <c r="N22" t="n">
-        <v>5.01</v>
+        <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>6350816580</v>
+        <v>49507586400</v>
       </c>
       <c r="P22" t="n">
-        <v>15900</v>
+        <v>63800</v>
       </c>
       <c r="Q22" t="n">
-        <v>6310</v>
+        <v>25600</v>
       </c>
       <c r="R22" t="n">
-        <v>-302000</v>
+        <v>-170000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 항생제 관련주 폭등 속 신풍제약 주가 부진. 바이러스 대장주로서의 기대감과 함께 주가 장난질에 대한 불만 표출.</t>
+          <t>주가 조작 신고 및 차명 거래 의혹 제기, 공매도에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['항생제 관련주', '주가 부진', '바이러스 대장주']</t>
+          <t>['주가 조작', '공매도', '차명 거래']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15000</v>
+        <v>15110</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.23%</t>
+          <t>'-9.58%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H23" t="n">
         <v>0.93</v>
@@ -2542,7 +2542,7 @@
         <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>31611378960</v>
+        <v>32023966055</v>
       </c>
       <c r="P23" t="n">
         <v>17590</v>
@@ -2581,6 +2581,98 @@
       <c r="Z23" t="inlineStr">
         <is>
           <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9880</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>'-10.26%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>62</v>
+      </c>
+      <c r="G24" t="n">
+        <v>341</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9750</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6472823690</v>
+      </c>
+      <c r="P24" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-302000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>미국 항생제 관련주 폭등 속 신풍제약 주가 부진. 바이러스 대장주로서의 기대감과 함께 주가 장난질에 대한 불만 표출.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['항생제 관련주', '주가 부진', '바이러스 대장주']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>019170</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261008_12.xlsx
+++ b/data/trending_integrated_20261008_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30861071720</v>
+        <v>30897045030</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14060</v>
+        <v>14170</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.26%</t>
+          <t>'+18.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H3" t="n">
         <v>4.43</v>
@@ -702,7 +702,7 @@
         <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>40714674685</v>
+        <v>41102117570</v>
       </c>
       <c r="P3" t="n">
         <v>14980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11290</v>
+        <v>11300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.27%</t>
+          <t>'+14.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>51376807035</v>
+        <v>51909681955</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13450</v>
+        <v>38400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.00%</t>
+          <t>'+6.08%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="H5" t="n">
-        <v>1.07</v>
+        <v>31.86</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12570</v>
+        <v>36200</v>
       </c>
       <c r="K5" t="n">
-        <v>12970</v>
+        <v>36250</v>
       </c>
       <c r="L5" t="n">
-        <v>14200</v>
+        <v>39850</v>
       </c>
       <c r="M5" t="n">
-        <v>12500</v>
+        <v>36000</v>
       </c>
       <c r="N5" t="n">
-        <v>1.88</v>
+        <v>31.78</v>
       </c>
       <c r="O5" t="n">
-        <v>76813148755</v>
+        <v>109134036975</v>
       </c>
       <c r="P5" t="n">
-        <v>22250</v>
+        <v>45000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6000</v>
+        <v>15530</v>
       </c>
       <c r="R5" t="n">
-        <v>-324000</v>
+        <v>199000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유증 물량 정리 후 주가 상승 기대감, 바이오스텝 및 HLB 승인 관련 논의.</t>
+          <t>JP모건의 기관/외국인 매수세 유입 및 추세적 상승세 확인. 하락장에서도 주가 방어 성공. 4만원 안착 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유증 물량', '바이오스텝', 'HLB 승인']</t>
+          <t>['기관 매수', '추세', '실적']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38475</v>
+        <v>6830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.28%</t>
+          <t>'+5.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H6" t="n">
-        <v>31.86</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36200</v>
+        <v>6460</v>
       </c>
       <c r="K6" t="n">
-        <v>36250</v>
+        <v>6930</v>
       </c>
       <c r="L6" t="n">
-        <v>39850</v>
+        <v>8390</v>
       </c>
       <c r="M6" t="n">
-        <v>36000</v>
+        <v>6730</v>
       </c>
       <c r="N6" t="n">
-        <v>31.78</v>
+        <v>0.31</v>
       </c>
       <c r="O6" t="n">
-        <v>107930775300</v>
+        <v>20027191740</v>
       </c>
       <c r="P6" t="n">
-        <v>45000</v>
+        <v>9680</v>
       </c>
       <c r="Q6" t="n">
-        <v>15530</v>
+        <v>371</v>
       </c>
       <c r="R6" t="n">
-        <v>199000</v>
+        <v>-25000</v>
       </c>
       <c r="S6" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JP모건 등 기관 및 외국인의 매수세 유입. 긍정적 추세 확인 및 실적 기대감.</t>
+          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기관 매수', '추세', '실적']</t>
+          <t>['관리종목', '해제', '호재']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6850</v>
+        <v>13250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.04%</t>
+          <t>'+5.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.31</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6460</v>
+        <v>12570</v>
       </c>
       <c r="K7" t="n">
-        <v>6930</v>
+        <v>12970</v>
       </c>
       <c r="L7" t="n">
-        <v>8390</v>
+        <v>14200</v>
       </c>
       <c r="M7" t="n">
-        <v>6730</v>
+        <v>12500</v>
       </c>
       <c r="N7" t="n">
-        <v>0.31</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>19859712660</v>
+        <v>78043171650</v>
       </c>
       <c r="P7" t="n">
-        <v>9680</v>
+        <v>22250</v>
       </c>
       <c r="Q7" t="n">
-        <v>371</v>
+        <v>6000</v>
       </c>
       <c r="R7" t="n">
-        <v>-25000</v>
+        <v>-324000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
+          <t>HLB제약의 비만 치료제 개발 기대감 및 유증 물량 소화 후 주가 상승 가능성 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['관리종목', '해제', '호재']</t>
+          <t>['비만 치료제', '유증', '바이오']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1731000</v>
+        <v>4485</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.12</v>
+        <v>1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>421</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>1379</v>
+        <v>157</v>
       </c>
       <c r="H8" t="n">
-        <v>49.59</v>
+        <v>4.46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1723000</v>
+        <v>4430</v>
       </c>
       <c r="K8" t="n">
-        <v>1722000</v>
+        <v>4650</v>
       </c>
       <c r="L8" t="n">
-        <v>1759000</v>
+        <v>4855</v>
       </c>
       <c r="M8" t="n">
-        <v>1722000</v>
+        <v>4185</v>
       </c>
       <c r="N8" t="n">
-        <v>49.71</v>
+        <v>3.27</v>
       </c>
       <c r="O8" t="n">
-        <v>2294277141500</v>
+        <v>83111160030</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>5470</v>
       </c>
       <c r="Q8" t="n">
-        <v>403000</v>
+        <v>2810</v>
       </c>
       <c r="R8" t="n">
-        <v>-25000</v>
+        <v>-469000</v>
       </c>
       <c r="S8" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 논란으로 인한 주주 불만. 정부의 정책 비판.</t>
+          <t>미국 항생제 회사 주가 폭등 및 WHO의 러시아 폐렴 관련 불확실성에 따른 투자 심리 혼조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '주주']</t>
+          <t>['항생제', 'WHO', '전염병']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45925</v>
+        <v>1724500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.05%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="E9" t="n">
-        <v>251</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>150</v>
+        <v>428</v>
       </c>
       <c r="G9" t="n">
-        <v>942</v>
+        <v>1407</v>
       </c>
       <c r="H9" t="n">
-        <v>13.39</v>
+        <v>49.59</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45900</v>
+        <v>1723000</v>
       </c>
       <c r="K9" t="n">
-        <v>45950</v>
+        <v>1722000</v>
       </c>
       <c r="L9" t="n">
-        <v>46500</v>
+        <v>1759000</v>
       </c>
       <c r="M9" t="n">
-        <v>45100</v>
+        <v>1722000</v>
       </c>
       <c r="N9" t="n">
-        <v>14.12</v>
+        <v>49.71</v>
       </c>
       <c r="O9" t="n">
-        <v>26999924875</v>
+        <v>2402986347500</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>403000</v>
       </c>
       <c r="R9" t="n">
-        <v>-12000</v>
+        <v>-25000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB 리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 긍정적 주가 전망.</t>
+          <t>솔리다임 관련 논란 및 중복 상장 의혹, 주가 하락에 대한 정부 및 경영진 비판.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['리보세라닙', '허가', '공매도']</t>
+          <t>['솔리다임', '중복 상장', '자사주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,130 +1292,130 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8220</v>
+        <v>45800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.36%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="G10" t="n">
-        <v>191</v>
+        <v>956</v>
       </c>
       <c r="H10" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8250</v>
+        <v>45900</v>
       </c>
       <c r="K10" t="n">
-        <v>8190</v>
+        <v>45950</v>
       </c>
       <c r="L10" t="n">
-        <v>8320</v>
+        <v>46500</v>
       </c>
       <c r="M10" t="n">
-        <v>8090</v>
+        <v>45100</v>
       </c>
       <c r="N10" t="n">
-        <v>26.55</v>
+        <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>11931504690</v>
+        <v>27428278750</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>8090</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-6000</v>
+        <v>-12000</v>
       </c>
       <c r="S10" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>HLB 리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 긍정적 주가 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['리보세라닙', '허가', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4385</v>
+        <v>8200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.19</v>
+        <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="H11" t="n">
-        <v>4.46</v>
+        <v>26.38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,60 +1423,60 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4430</v>
+        <v>8250</v>
       </c>
       <c r="K11" t="n">
-        <v>4650</v>
+        <v>8190</v>
       </c>
       <c r="L11" t="n">
-        <v>4855</v>
+        <v>8320</v>
       </c>
       <c r="M11" t="n">
-        <v>4185</v>
+        <v>8090</v>
       </c>
       <c r="N11" t="n">
-        <v>3.27</v>
+        <v>26.55</v>
       </c>
       <c r="O11" t="n">
-        <v>81743402889</v>
+        <v>12483709520</v>
       </c>
       <c r="P11" t="n">
-        <v>5470</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>2810</v>
+        <v>8090</v>
       </c>
       <c r="R11" t="n">
-        <v>-469000</v>
+        <v>-6000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 전염병 관련 불확실성 언급. 국제 분위기상 주가 상승 기대감.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['항생제', 'WHO', '전염병']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G12" t="n">
-        <v>1713</v>
+        <v>1710</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1524,13 +1524,13 @@
         <v>270000</v>
       </c>
       <c r="M12" t="n">
-        <v>265500</v>
+        <v>265000</v>
       </c>
       <c r="N12" t="n">
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>2321763836500</v>
+        <v>2465088056750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자 107조 분기 영업이익에도 불구하고 주가 부양되지 않는 현실에 대한 불만.</t>
+          <t>삼성전자 107조 영업이익 달성에도 주가 부양 실패, 실적 대비 주가 하락에 대한 불만 고조.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16850</v>
+        <v>16810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.83%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="H13" t="n">
         <v>9.460000000000001</v>
@@ -1622,7 +1622,7 @@
         <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>29404525430</v>
+        <v>30122782100</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 의혹, 공매도 과열 및 대차 해지 중요성 강조.</t>
+          <t>공매도 및 주가 조작 의혹 제기, 기관 투자자에 대한 불신과 주주 호소문 반복 게시.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '대차 해지']</t>
+          <t>['공매도', '주가 조작', '주주 호소']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>33239404355</v>
+        <v>34198085455</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>증권사 애널리스트 및 방송, 유튜브, 리딩방의 투자 조언에 대한 불신. 조선주 전반의 부진.</t>
+          <t>조선주 전반의 하락세와 수주 관련 부정적 뉴스, 증권사 목표가 하향 조정에 따른 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['애널리스트', '조선주', '투자']</t>
+          <t>['조선주', '수주', '증권사']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>232000</v>
+        <v>230500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.73%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.65</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="H15" t="n">
         <v>3.47</v>
@@ -1806,7 +1806,7 @@
         <v>4.12</v>
       </c>
       <c r="O15" t="n">
-        <v>36216746750</v>
+        <v>37358519250</v>
       </c>
       <c r="P15" t="n">
         <v>1233000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼천당제약, 아일리아 영업이익 전망 및 연기금 매수 동향. 릴레이 계약공시 및 공매도 금지 관련 긍정적 뉴스.</t>
+          <t>공매도 금지 조치 및 릴레이 계약 공시 가능성에 따른 기대감. 연기금의 7일 연속 매수세 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['아일리아', '연기금', '계약공시']</t>
+          <t>['공매도 금지', '계약 공시', '연기금']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,171 +1851,171 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13160</v>
+        <v>28350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.57%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.15</v>
+        <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>273</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
-        <v>139</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>887</v>
+        <v>151</v>
       </c>
       <c r="H16" t="n">
-        <v>0.09</v>
+        <v>10.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13790</v>
+        <v>29800</v>
       </c>
       <c r="K16" t="n">
-        <v>13410</v>
+        <v>29900</v>
       </c>
       <c r="L16" t="n">
-        <v>13940</v>
+        <v>30000</v>
       </c>
       <c r="M16" t="n">
-        <v>11600</v>
+        <v>28250</v>
       </c>
       <c r="N16" t="n">
-        <v>0.24</v>
+        <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>37436068820</v>
+        <v>50501168675</v>
       </c>
       <c r="P16" t="n">
-        <v>28700</v>
+        <v>75900</v>
       </c>
       <c r="Q16" t="n">
-        <v>11600</v>
+        <v>15960</v>
       </c>
       <c r="R16" t="n">
-        <v>17000</v>
+        <v>-380000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>덕산넵코어스의 사기 상장 의혹 및 중복 상장 예외 허용에 대한 비판. 금융당국 및 정부 불신.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['사기 상장', '중복 상장', '금융당국']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28400</v>
+        <v>7430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>-2.03</v>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="G17" t="n">
-        <v>142</v>
+        <v>444</v>
       </c>
       <c r="H17" t="n">
-        <v>10.02</v>
+        <v>3.09</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>7820</v>
       </c>
       <c r="K17" t="n">
-        <v>29900</v>
+        <v>8080</v>
       </c>
       <c r="L17" t="n">
-        <v>30000</v>
+        <v>8510</v>
       </c>
       <c r="M17" t="n">
-        <v>28400</v>
+        <v>7170</v>
       </c>
       <c r="N17" t="n">
-        <v>10.78</v>
+        <v>5.12</v>
       </c>
       <c r="O17" t="n">
-        <v>47072411200</v>
+        <v>80297723135</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>23500</v>
       </c>
       <c r="Q17" t="n">
-        <v>15960</v>
+        <v>2890</v>
       </c>
       <c r="R17" t="n">
-        <v>-380000</v>
+        <v>-501000</v>
       </c>
       <c r="S17" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>삼표시멘트의 부동산 개발 관련 기대감과 PF 대주단 구성 소식에도 불구하고 주가 하락.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['부동산 개발', 'PF', '시멘트']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,43 +2023,43 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7390</v>
+        <v>16890</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.50%</t>
+          <t>'-5.85%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-2.03</v>
+        <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G18" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="H18" t="n">
-        <v>3.09</v>
+        <v>3.97</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7820</v>
+        <v>17940</v>
       </c>
       <c r="K18" t="n">
-        <v>8080</v>
+        <v>17770</v>
       </c>
       <c r="L18" t="n">
-        <v>8510</v>
+        <v>17940</v>
       </c>
       <c r="M18" t="n">
-        <v>7170</v>
+        <v>16800</v>
       </c>
       <c r="N18" t="n">
-        <v>5.12</v>
+        <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>79769156930</v>
+        <v>80852658900</v>
       </c>
       <c r="P18" t="n">
-        <v>23500</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>2890</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-501000</v>
+        <v>-168000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>삼표시멘트, 3-4조 규모 본PF 및 부동산주 관련 언급. 하지만 주가 하락 및 개인 투자자 매도에 대한 부정적 시각.</t>
+          <t>미국 광통신주 하락세 영향 및 프로그램 매매 불안정성으로 인한 대한광통신 주가 하락.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['본PF', '부동산주', '주가 하락']</t>
+          <t>['광통신', '프로그램 매매', '미국 증시']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16920</v>
+        <v>12950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.69%</t>
+          <t>'-6.09%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.95</v>
+        <v>-0.15</v>
       </c>
       <c r="E19" t="n">
-        <v>96</v>
+        <v>282</v>
       </c>
       <c r="F19" t="n">
-        <v>64</v>
+        <v>143</v>
       </c>
       <c r="G19" t="n">
-        <v>442</v>
+        <v>911</v>
       </c>
       <c r="H19" t="n">
-        <v>3.97</v>
+        <v>0.09</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17940</v>
+        <v>13790</v>
       </c>
       <c r="K19" t="n">
-        <v>17770</v>
+        <v>13410</v>
       </c>
       <c r="L19" t="n">
-        <v>17940</v>
+        <v>13940</v>
       </c>
       <c r="M19" t="n">
-        <v>16800</v>
+        <v>11600</v>
       </c>
       <c r="N19" t="n">
-        <v>4.92</v>
+        <v>0.24</v>
       </c>
       <c r="O19" t="n">
-        <v>78856961130</v>
+        <v>40621246380</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>28700</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>11600</v>
       </c>
       <c r="R19" t="n">
-        <v>-168000</v>
+        <v>17000</v>
       </c>
       <c r="S19" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 하락에 따른 대한광통신 주가 변동성에 대한 우려. 공매도 관련 언급.</t>
+          <t>덕산넵코어스의 사기 상장 및 중복 상장 의혹 제기, 금감원 신고 및 국민권익위 조사 요청.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '주가 하락', '공매도']</t>
+          <t>['중복 상장', '사기 상장', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75700</v>
+        <v>75400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.96%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="F20" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G20" t="n">
-        <v>947</v>
+        <v>1020</v>
       </c>
       <c r="H20" t="n">
         <v>22.49</v>
@@ -2260,13 +2260,13 @@
         <v>79600</v>
       </c>
       <c r="M20" t="n">
-        <v>75600</v>
+        <v>75300</v>
       </c>
       <c r="N20" t="n">
         <v>22.59</v>
       </c>
       <c r="O20" t="n">
-        <v>161725188150</v>
+        <v>169456638200</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 한미 텍사스 가스발전 확정 및 원전 관련 뉴스 언급. 하지만 주가 하락에 대한 불만과 공매도 관련 언급.</t>
+          <t>미국 가스 발전 확정 뉴스에도 불구하고 원전 관련 부정적 전망 및 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['원전', '가스 발전', '수출']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4865</v>
+        <v>4840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.62%</t>
+          <t>'-7.10%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H21" t="n">
         <v>4.65</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>61994164177</v>
+        <v>62463719146</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53600</v>
+        <v>53300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.75%</t>
+          <t>'-8.26%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F22" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G22" t="n">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2450,7 +2450,7 @@
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>49507586400</v>
+        <v>50386870300</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 조작 신고 및 차명 거래 의혹 제기, 공매도에 대한 부정적 시각.</t>
+          <t>국내 시장 석권 준비 및 미국 비만주 급등 속에서 에페 식약처 승인에도 불구하고 이해 안 되는 급락 발생. 주가 조작 및 차명 거래 의심 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '차명 거래']</t>
+          <t>['비만약', '식약처 승인', '주가 조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15110</v>
+        <v>15090</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.58%</t>
+          <t>'-9.69%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H23" t="n">
         <v>0.93</v>
@@ -2542,7 +2542,7 @@
         <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>32023966055</v>
+        <v>32266175350</v>
       </c>
       <c r="P23" t="n">
         <v>17590</v>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9880</v>
+        <v>9860</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.26%</t>
+          <t>'-10.45%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2605,10 +2605,10 @@
         <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>6472823690</v>
+        <v>6573052670</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_12.xlsx
+++ b/data/trending_integrated_20261008_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30897045030</v>
+        <v>30915792040</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14170</v>
+        <v>11460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.18%</t>
+          <t>'+15.99%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="H3" t="n">
-        <v>4.43</v>
+        <v>37.45</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11990</v>
+        <v>9880</v>
       </c>
       <c r="K3" t="n">
-        <v>14330</v>
+        <v>10030</v>
       </c>
       <c r="L3" t="n">
-        <v>14980</v>
+        <v>11540</v>
       </c>
       <c r="M3" t="n">
-        <v>13070</v>
+        <v>9850</v>
       </c>
       <c r="N3" t="n">
-        <v>4.66</v>
+        <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>41102117570</v>
+        <v>54364463045</v>
       </c>
       <c r="P3" t="n">
-        <v>14980</v>
+        <v>19150</v>
       </c>
       <c r="Q3" t="n">
-        <v>6500</v>
+        <v>3445</v>
       </c>
       <c r="R3" t="n">
-        <v>48000</v>
+        <v>219000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>191000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성전기향 차세대 유리기판 핵심 부품 공급 계약 및 공동 개발 뉴스 기반 강세. 매출 및 영업이익 증가 전망.</t>
+          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스본더', '공급']</t>
+          <t>['전구체', '양극재', '매출']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11300</v>
+        <v>13860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.37%</t>
+          <t>'+15.60%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="H4" t="n">
-        <v>37.45</v>
+        <v>4.43</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9880</v>
+        <v>11990</v>
       </c>
       <c r="K4" t="n">
-        <v>10030</v>
+        <v>14330</v>
       </c>
       <c r="L4" t="n">
-        <v>11540</v>
+        <v>14980</v>
       </c>
       <c r="M4" t="n">
-        <v>9850</v>
+        <v>13070</v>
       </c>
       <c r="N4" t="n">
-        <v>37.41</v>
+        <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>51909681955</v>
+        <v>41746159955</v>
       </c>
       <c r="P4" t="n">
-        <v>19150</v>
+        <v>14980</v>
       </c>
       <c r="Q4" t="n">
-        <v>3445</v>
+        <v>6500</v>
       </c>
       <c r="R4" t="n">
-        <v>219000</v>
+        <v>48000</v>
       </c>
       <c r="S4" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 부품 공급 계약 및 공동 개발 뉴스 기반 강세. 매출 및 영업이익 증가 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전구체', '양극재', '매출']</t>
+          <t>['유리기판', '글라스본더', '공급']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38400</v>
+        <v>6880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.08%</t>
+          <t>'+6.50%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H5" t="n">
-        <v>31.86</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>36200</v>
+        <v>6460</v>
       </c>
       <c r="K5" t="n">
-        <v>36250</v>
+        <v>6930</v>
       </c>
       <c r="L5" t="n">
-        <v>39850</v>
+        <v>8390</v>
       </c>
       <c r="M5" t="n">
-        <v>36000</v>
+        <v>6730</v>
       </c>
       <c r="N5" t="n">
-        <v>31.78</v>
+        <v>0.31</v>
       </c>
       <c r="O5" t="n">
-        <v>109134036975</v>
+        <v>20054267360</v>
       </c>
       <c r="P5" t="n">
-        <v>45000</v>
+        <v>9680</v>
       </c>
       <c r="Q5" t="n">
-        <v>15530</v>
+        <v>371</v>
       </c>
       <c r="R5" t="n">
-        <v>199000</v>
+        <v>-25000</v>
       </c>
       <c r="S5" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>JP모건의 기관/외국인 매수세 유입 및 추세적 상승세 확인. 하락장에서도 주가 방어 성공. 4만원 안착 기대감.</t>
+          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['기관 매수', '추세', '실적']</t>
+          <t>['관리종목', '해제', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6830</v>
+        <v>38450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.73%</t>
+          <t>'+6.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>31.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6460</v>
+        <v>36200</v>
       </c>
       <c r="K6" t="n">
-        <v>6930</v>
+        <v>36250</v>
       </c>
       <c r="L6" t="n">
-        <v>8390</v>
+        <v>39850</v>
       </c>
       <c r="M6" t="n">
-        <v>6730</v>
+        <v>36000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.31</v>
+        <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>20027191740</v>
+        <v>109576864825</v>
       </c>
       <c r="P6" t="n">
-        <v>9680</v>
+        <v>45000</v>
       </c>
       <c r="Q6" t="n">
-        <v>371</v>
+        <v>15530</v>
       </c>
       <c r="R6" t="n">
-        <v>-25000</v>
+        <v>199000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
+          <t>JP모건 등 기관 및 외국인 매수세 유입과 추세적 상승에 대한 긍정적 전망, 하락장에서도 주가 버텨준 점 강조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['관리종목', '해제', '호재']</t>
+          <t>['기관매수', '추세', '외국인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13250</v>
+        <v>13260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.41%</t>
+          <t>'+5.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H7" t="n">
         <v>1.07</v>
@@ -1070,7 +1070,7 @@
         <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>78043171650</v>
+        <v>79074825620</v>
       </c>
       <c r="P7" t="n">
         <v>22250</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HLB제약의 비만 치료제 개발 기대감 및 유증 물량 소화 후 주가 상승 가능성 제기.</t>
+          <t>유증 물량 정리 및 바이오스텝 관련 긍정적 언급과 함께 1차 목표가 3만원 제시, HLB 승인 시 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['비만 치료제', '유증', '바이오']</t>
+          <t>['유증', '바이오스텝', 'HLB']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4485</v>
+        <v>4490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.24%</t>
+          <t>'+1.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G8" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H8" t="n">
         <v>4.46</v>
@@ -1162,7 +1162,7 @@
         <v>3.27</v>
       </c>
       <c r="O8" t="n">
-        <v>83111160030</v>
+        <v>84494466029</v>
       </c>
       <c r="P8" t="n">
         <v>5470</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 주가 폭등 및 WHO의 러시아 폐렴 관련 불확실성에 따른 투자 심리 혼조.</t>
+          <t>미국 항생제 보유 회사 주가 폭등 속보와 WHO의 러시아 폐렴 관련 상황 파악 미흡 소식에 따른 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['항생제', 'WHO', '전염병']</t>
+          <t>['항생제', '폐렴', 'WHO']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1724500</v>
+        <v>13870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.09%</t>
+          <t>'+0.58%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>302</v>
       </c>
       <c r="F9" t="n">
-        <v>428</v>
+        <v>149</v>
       </c>
       <c r="G9" t="n">
-        <v>1407</v>
+        <v>945</v>
       </c>
       <c r="H9" t="n">
-        <v>49.59</v>
+        <v>0.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1723000</v>
+        <v>13790</v>
       </c>
       <c r="K9" t="n">
-        <v>1722000</v>
+        <v>13410</v>
       </c>
       <c r="L9" t="n">
-        <v>1759000</v>
+        <v>14140</v>
       </c>
       <c r="M9" t="n">
-        <v>1722000</v>
+        <v>11600</v>
       </c>
       <c r="N9" t="n">
-        <v>49.71</v>
+        <v>0.24</v>
       </c>
       <c r="O9" t="n">
-        <v>2402986347500</v>
+        <v>49674018535</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>28700</v>
       </c>
       <c r="Q9" t="n">
-        <v>403000</v>
+        <v>11600</v>
       </c>
       <c r="R9" t="n">
-        <v>-25000</v>
+        <v>17000</v>
       </c>
       <c r="S9" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 관련 논란 및 중복 상장 의혹, 주가 하락에 대한 정부 및 경영진 비판.</t>
+          <t>덕산넵코어스의 사기 상장 및 중복 상장 의혹 제기, 금감원 신고 및 국민권익위 조사 요청.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복 상장', '자사주']</t>
+          <t>['중복 상장', '사기 상장', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45800</v>
+        <v>1724000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>260</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>153</v>
+        <v>426</v>
       </c>
       <c r="G10" t="n">
-        <v>956</v>
+        <v>1416</v>
       </c>
       <c r="H10" t="n">
-        <v>13.39</v>
+        <v>49.59</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45900</v>
+        <v>1723000</v>
       </c>
       <c r="K10" t="n">
-        <v>45950</v>
+        <v>1722000</v>
       </c>
       <c r="L10" t="n">
-        <v>46500</v>
+        <v>1759000</v>
       </c>
       <c r="M10" t="n">
-        <v>45100</v>
+        <v>1722000</v>
       </c>
       <c r="N10" t="n">
-        <v>14.12</v>
+        <v>49.71</v>
       </c>
       <c r="O10" t="n">
-        <v>27428278750</v>
+        <v>2466388892000</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>403000</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-25000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB 리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 긍정적 주가 전망.</t>
+          <t>솔리다임 상장 이슈와 관련된 논란 및 주주 통수 의혹, 정부 정책에 대한 불만과 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보세라닙', '허가', '공매도']</t>
+          <t>['솔리다임', '상장', '자사주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8200</v>
+        <v>45900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>73</v>
+        <v>263</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="G11" t="n">
-        <v>199</v>
+        <v>971</v>
       </c>
       <c r="H11" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8250</v>
+        <v>45900</v>
       </c>
       <c r="K11" t="n">
-        <v>8190</v>
+        <v>45950</v>
       </c>
       <c r="L11" t="n">
-        <v>8320</v>
+        <v>46500</v>
       </c>
       <c r="M11" t="n">
-        <v>8090</v>
+        <v>45100</v>
       </c>
       <c r="N11" t="n">
-        <v>26.55</v>
+        <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>12483709520</v>
+        <v>28106934675</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>8090</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-6000</v>
+        <v>-12000</v>
       </c>
       <c r="S11" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>리보세라닙 병용요법 허가 기대감과 공매도 세력 발악 언급, 2026년 연말 30만 목표 및 우상향 차트 시작 주장.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['리보세라닙', '공매도', '허가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>265500</v>
+        <v>8240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>511</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>1710</v>
+        <v>208</v>
       </c>
       <c r="H12" t="n">
-        <v>46.38</v>
+        <v>26.38</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>268500</v>
+        <v>8250</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>8190</v>
       </c>
       <c r="L12" t="n">
-        <v>270000</v>
+        <v>8320</v>
       </c>
       <c r="M12" t="n">
-        <v>265000</v>
+        <v>8090</v>
       </c>
       <c r="N12" t="n">
-        <v>46.37</v>
+        <v>26.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2465088056750</v>
+        <v>12773256955</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>8090</v>
       </c>
       <c r="R12" t="n">
-        <v>36000</v>
+        <v>-6000</v>
       </c>
       <c r="S12" t="n">
-        <v>-328000</v>
+        <v>44000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자 107조 영업이익 달성에도 주가 부양 실패, 실적 대비 주가 하락에 대한 불만 고조.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '실적']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16810</v>
+        <v>266250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-0.84%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>89</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>524</v>
       </c>
       <c r="G13" t="n">
-        <v>412</v>
+        <v>1736</v>
       </c>
       <c r="H13" t="n">
-        <v>9.460000000000001</v>
+        <v>46.38</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17340</v>
+        <v>268500</v>
       </c>
       <c r="K13" t="n">
-        <v>17190</v>
+        <v>269500</v>
       </c>
       <c r="L13" t="n">
-        <v>17220</v>
+        <v>270000</v>
       </c>
       <c r="M13" t="n">
-        <v>16710</v>
+        <v>265000</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>30122782100</v>
+        <v>2519079486000</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>70000</v>
+        <v>36000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>-328000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 및 주가 조작 의혹 제기, 기관 투자자에 대한 불신과 주주 호소문 반복 게시.</t>
+          <t>삼성전자 107조 영업이익에도 주가 부양이 되지 않는 현실에 대한 불만과 실적 대비 주가 부양 실패 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '주가 조작', '주주 호소']</t>
+          <t>['영업이익', '주가 부양', '실적']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18925</v>
+        <v>16850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.15%</t>
+          <t>'-2.83%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G14" t="n">
-        <v>325</v>
+        <v>424</v>
       </c>
       <c r="H14" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19540</v>
+        <v>17340</v>
       </c>
       <c r="K14" t="n">
-        <v>19490</v>
+        <v>17190</v>
       </c>
       <c r="L14" t="n">
-        <v>19500</v>
+        <v>17220</v>
       </c>
       <c r="M14" t="n">
-        <v>18910</v>
+        <v>16710</v>
       </c>
       <c r="N14" t="n">
-        <v>27.67</v>
+        <v>9.5</v>
       </c>
       <c r="O14" t="n">
-        <v>34198085455</v>
+        <v>30891753595</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>18440</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-255000</v>
+        <v>70000</v>
       </c>
       <c r="S14" t="n">
-        <v>-24000</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>조선주 전반의 하락세와 수주 관련 부정적 뉴스, 증권사 목표가 하향 조정에 따른 투자 심리 악화.</t>
+          <t>공매도 및 주가 조작 의혹 제기, 기관 투자자에 대한 불신과 주주 호소문 반복 게시.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '수주', '증권사']</t>
+          <t>['공매도', '주가 조작', '주주 호소']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>230500</v>
+        <v>18980</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-2.87%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F15" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>675</v>
+        <v>329</v>
       </c>
       <c r="H15" t="n">
-        <v>3.47</v>
+        <v>27.68</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>241000</v>
+        <v>19540</v>
       </c>
       <c r="K15" t="n">
-        <v>227000</v>
+        <v>19490</v>
       </c>
       <c r="L15" t="n">
-        <v>239500</v>
+        <v>19500</v>
       </c>
       <c r="M15" t="n">
-        <v>210500</v>
+        <v>18910</v>
       </c>
       <c r="N15" t="n">
-        <v>4.12</v>
+        <v>27.67</v>
       </c>
       <c r="O15" t="n">
-        <v>37358519250</v>
+        <v>34592863200</v>
       </c>
       <c r="P15" t="n">
-        <v>1233000</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>120000</v>
+        <v>18440</v>
       </c>
       <c r="R15" t="n">
-        <v>5000</v>
+        <v>-255000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>-24000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 금지 조치 및 릴레이 계약 공시 가능성에 따른 기대감. 연기금의 7일 연속 매수세 확인.</t>
+          <t>증권사 애널리스트 및 리딩방 정보에 대한 불신과 조선주 전반의 실적 부진 및 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도 금지', '계약 공시', '연기금']</t>
+          <t>['조선주', '실적', '수주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28350</v>
+        <v>28400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H16" t="n">
         <v>10.02</v>
@@ -1898,7 +1898,7 @@
         <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>50501168675</v>
+        <v>51042004100</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7430</v>
+        <v>229500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.03</v>
+        <v>-0.65</v>
       </c>
       <c r="E17" t="n">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="F17" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>444</v>
+        <v>678</v>
       </c>
       <c r="H17" t="n">
-        <v>3.09</v>
+        <v>3.47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7820</v>
+        <v>241000</v>
       </c>
       <c r="K17" t="n">
-        <v>8080</v>
+        <v>227000</v>
       </c>
       <c r="L17" t="n">
-        <v>8510</v>
+        <v>239500</v>
       </c>
       <c r="M17" t="n">
-        <v>7170</v>
+        <v>210500</v>
       </c>
       <c r="N17" t="n">
-        <v>5.12</v>
+        <v>4.12</v>
       </c>
       <c r="O17" t="n">
-        <v>80297723135</v>
+        <v>37810128250</v>
       </c>
       <c r="P17" t="n">
-        <v>23500</v>
+        <v>1233000</v>
       </c>
       <c r="Q17" t="n">
-        <v>2890</v>
+        <v>120000</v>
       </c>
       <c r="R17" t="n">
-        <v>-501000</v>
+        <v>5000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>삼표시멘트의 부동산 개발 관련 기대감과 PF 대주단 구성 소식에도 불구하고 주가 하락.</t>
+          <t>공매도 금지 조치 및 릴레이 계약 공시 가능성에 따른 기대감. 연기금의 7일 연속 매수세 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['부동산 개발', 'PF', '시멘트']</t>
+          <t>['공매도 금지', '계약 공시', '연기금']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16890</v>
+        <v>17020</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.85%</t>
+          <t>'-5.13%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>80852658900</v>
+        <v>81953599900</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2091,10 +2091,10 @@
         <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-168000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12950</v>
+        <v>7380</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.09%</t>
+          <t>'-5.63%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.15</v>
+        <v>-2.03</v>
       </c>
       <c r="E19" t="n">
-        <v>282</v>
+        <v>166</v>
       </c>
       <c r="F19" t="n">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
-        <v>911</v>
+        <v>450</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09</v>
+        <v>3.09</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13790</v>
+        <v>7820</v>
       </c>
       <c r="K19" t="n">
-        <v>13410</v>
+        <v>8080</v>
       </c>
       <c r="L19" t="n">
-        <v>13940</v>
+        <v>8510</v>
       </c>
       <c r="M19" t="n">
-        <v>11600</v>
+        <v>7170</v>
       </c>
       <c r="N19" t="n">
-        <v>0.24</v>
+        <v>5.12</v>
       </c>
       <c r="O19" t="n">
-        <v>40621246380</v>
+        <v>80608538435</v>
       </c>
       <c r="P19" t="n">
-        <v>28700</v>
+        <v>23500</v>
       </c>
       <c r="Q19" t="n">
-        <v>11600</v>
+        <v>2890</v>
       </c>
       <c r="R19" t="n">
-        <v>17000</v>
+        <v>-501000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>덕산넵코어스의 사기 상장 및 중복 상장 의혹 제기, 금감원 신고 및 국민권익위 조사 요청.</t>
+          <t>삼표시멘트의 부동산 개발 관련 기대감과 PF 대주단 구성 소식에도 불구하고 주가 하락.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['중복 상장', '사기 상장', '공매도']</t>
+          <t>['부동산 개발', 'PF', '시멘트']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -2223,21 +2223,21 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75400</v>
+        <v>75700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-5.96%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="F20" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G20" t="n">
         <v>1020</v>
@@ -2266,7 +2266,7 @@
         <v>22.59</v>
       </c>
       <c r="O20" t="n">
-        <v>169456638200</v>
+        <v>172943749100</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 가스 발전 확정 뉴스에도 불구하고 원전 관련 부정적 전망 및 주가 하락세 지속.</t>
+          <t>미국 텍사스 가스 발전 확정 및 한국 관세 인하 가능성에도 불구하고 원전 관련 부정적 전망과 하락세에 대한 실망감.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '가스 발전', '수출']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4840</v>
+        <v>4855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.10%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2332,7 +2332,7 @@
         <v>58</v>
       </c>
       <c r="G21" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H21" t="n">
         <v>4.65</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>62463719146</v>
+        <v>62732296378</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 대량 매도 우려, 주가 급등 기대와 단기 매도세 혼재.</t>
+          <t>전환사채 발행 및 장내 매도 물량 부담으로 인한 초대형 악재 발생, 주가 급락에 대한 경고와 속지 말자는 주장.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '대량 매도', '주가 전망']</t>
+          <t>['전환사채', '악재', '장내매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53300</v>
+        <v>53800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.26%</t>
+          <t>'-7.40%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F22" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G22" t="n">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2450,7 +2450,7 @@
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>50386870300</v>
+        <v>50808442900</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>국내 시장 석권 준비 및 미국 비만주 급등 속에서 에페 식약처 승인에도 불구하고 이해 안 되는 급락 발생. 주가 조작 및 차명 거래 의심 제기.</t>
+          <t>국내 시장 석권 준비 및 미국 비만주 급등 소식에도 불구하고 이해할 수 없는 급락과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비만약', '식약처 승인', '주가 조작']</t>
+          <t>['비만주', '주가조작', '급락']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15090</v>
+        <v>15240</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.69%</t>
+          <t>'-8.80%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
         <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H23" t="n">
         <v>0.93</v>
@@ -2542,7 +2542,7 @@
         <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>32266175350</v>
+        <v>32483225680</v>
       </c>
       <c r="P23" t="n">
         <v>17590</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9860</v>
+        <v>9900</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.45%</t>
+          <t>'-10.08%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" t="n">
         <v>61</v>
       </c>
       <c r="G24" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>6573052670</v>
+        <v>6647050960</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_12.xlsx
+++ b/data/trending_integrated_20261008_12.xlsx
@@ -584,7 +584,7 @@
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30915792040</v>
+        <v>30924146480</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11460</v>
+        <v>13950</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.99%</t>
+          <t>'+16.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04</v>
+        <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="H3" t="n">
-        <v>37.45</v>
+        <v>4.43</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9880</v>
+        <v>11990</v>
       </c>
       <c r="K3" t="n">
-        <v>10030</v>
+        <v>14330</v>
       </c>
       <c r="L3" t="n">
-        <v>11540</v>
+        <v>14980</v>
       </c>
       <c r="M3" t="n">
-        <v>9850</v>
+        <v>13070</v>
       </c>
       <c r="N3" t="n">
-        <v>37.41</v>
+        <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>54364463045</v>
+        <v>42088796855</v>
       </c>
       <c r="P3" t="n">
-        <v>19150</v>
+        <v>14980</v>
       </c>
       <c r="Q3" t="n">
-        <v>3445</v>
+        <v>6500</v>
       </c>
       <c r="R3" t="n">
-        <v>219000</v>
+        <v>48000</v>
       </c>
       <c r="S3" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 부품 공급 계약 및 공동 개발 뉴스 기반 강세. 매출 및 영업이익 증가 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['전구체', '양극재', '매출']</t>
+          <t>['유리기판', '글라스본더', '공급']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13860</v>
+        <v>11400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.60%</t>
+          <t>'+15.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="H4" t="n">
-        <v>4.43</v>
+        <v>37.45</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11990</v>
+        <v>9880</v>
       </c>
       <c r="K4" t="n">
-        <v>14330</v>
+        <v>10030</v>
       </c>
       <c r="L4" t="n">
-        <v>14980</v>
+        <v>11540</v>
       </c>
       <c r="M4" t="n">
-        <v>13070</v>
+        <v>9850</v>
       </c>
       <c r="N4" t="n">
-        <v>4.66</v>
+        <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>41746159955</v>
+        <v>55870000645</v>
       </c>
       <c r="P4" t="n">
-        <v>14980</v>
+        <v>19150</v>
       </c>
       <c r="Q4" t="n">
-        <v>6500</v>
+        <v>3445</v>
       </c>
       <c r="R4" t="n">
-        <v>48000</v>
+        <v>219000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>191000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전기향 차세대 유리기판 핵심 부품 공급 계약 및 공동 개발 뉴스 기반 강세. 매출 및 영업이익 증가 전망.</t>
+          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스본더', '공급']</t>
+          <t>['전구체', '양극재', '매출']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6880</v>
+        <v>6850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.50%</t>
+          <t>'+6.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0.31</v>
       </c>
       <c r="O5" t="n">
-        <v>20054267360</v>
+        <v>20200395015</v>
       </c>
       <c r="P5" t="n">
         <v>9680</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>관리종목 해제 기대감 및 불확실성 악재 해소 분위기 속 상승 기대. 그러나 거래량 부진 및 가격 하락 지속.</t>
+          <t>관리종목 해제 및 중견소속부 변경이라는 호재가 언급되었으나, 기대감만 있고 구체적인 근거 제시 부족. 주가 급등 후 조정 양상.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['관리종목', '해제', '호재']</t>
+          <t>['관리종목 해제', '호재', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38450</v>
+        <v>14620</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.22%</t>
+          <t>'+6.02%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>334</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="G6" t="n">
-        <v>181</v>
+        <v>964</v>
       </c>
       <c r="H6" t="n">
-        <v>31.86</v>
+        <v>0.09</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36200</v>
+        <v>13790</v>
       </c>
       <c r="K6" t="n">
-        <v>36250</v>
+        <v>13410</v>
       </c>
       <c r="L6" t="n">
-        <v>39850</v>
+        <v>14680</v>
       </c>
       <c r="M6" t="n">
-        <v>36000</v>
+        <v>11600</v>
       </c>
       <c r="N6" t="n">
-        <v>31.78</v>
+        <v>0.24</v>
       </c>
       <c r="O6" t="n">
-        <v>109576864825</v>
+        <v>65984389060</v>
       </c>
       <c r="P6" t="n">
-        <v>45000</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>15530</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>199000</v>
+        <v>17000</v>
       </c>
       <c r="S6" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JP모건 등 기관 및 외국인 매수세 유입과 추세적 상승에 대한 긍정적 전망, 하락장에서도 주가 버텨준 점 강조.</t>
+          <t>중복 상장 및 무차별 공매도 관련 금융당국 조사 요청. 주가 조작 및 사기 상장 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기관매수', '추세', '외국인']</t>
+          <t>['중복 상장', '공매도', '금융당국']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13260</v>
+        <v>38300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.49%</t>
+          <t>'+5.80%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>31.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12570</v>
+        <v>36200</v>
       </c>
       <c r="K7" t="n">
-        <v>12970</v>
+        <v>36250</v>
       </c>
       <c r="L7" t="n">
-        <v>14200</v>
+        <v>39850</v>
       </c>
       <c r="M7" t="n">
-        <v>12500</v>
+        <v>36000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>79074825620</v>
+        <v>111305423850</v>
       </c>
       <c r="P7" t="n">
-        <v>22250</v>
+        <v>45000</v>
       </c>
       <c r="Q7" t="n">
-        <v>6000</v>
+        <v>15530</v>
       </c>
       <c r="R7" t="n">
-        <v>-324000</v>
+        <v>199000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유증 물량 정리 및 바이오스텝 관련 긍정적 언급과 함께 1차 목표가 3만원 제시, HLB 승인 시 동반 상승 기대.</t>
+          <t>JP모건 등 기관 및 외국인 매수세 유입과 추세적 상승에 대한 긍정적 전망, 하락장에서도 주가 버텨준 점 강조.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유증', '바이오스텝', 'HLB']</t>
+          <t>['기관매수', '추세', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4490</v>
+        <v>13160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'+4.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.19</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="H8" t="n">
-        <v>4.46</v>
+        <v>1.07</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4430</v>
+        <v>12570</v>
       </c>
       <c r="K8" t="n">
-        <v>4650</v>
+        <v>12970</v>
       </c>
       <c r="L8" t="n">
-        <v>4855</v>
+        <v>14200</v>
       </c>
       <c r="M8" t="n">
-        <v>4185</v>
+        <v>12500</v>
       </c>
       <c r="N8" t="n">
-        <v>3.27</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>84494466029</v>
+        <v>80515960620</v>
       </c>
       <c r="P8" t="n">
-        <v>5470</v>
+        <v>22250</v>
       </c>
       <c r="Q8" t="n">
-        <v>2810</v>
+        <v>6000</v>
       </c>
       <c r="R8" t="n">
-        <v>-469000</v>
+        <v>-324000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등 속보와 WHO의 러시아 폐렴 관련 상황 파악 미흡 소식에 따른 기대감.</t>
+          <t>유증 물량 정리 완료 후 상승 기대. 바이오스텝 관련 기대감, 1차 목표가 3만원 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', 'WHO']</t>
+          <t>['유증 물량', '바이오스텝', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13870</v>
+        <v>4465</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.58%</t>
+          <t>'+0.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.15</v>
+        <v>1.19</v>
       </c>
       <c r="E9" t="n">
-        <v>302</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
-        <v>945</v>
+        <v>161</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09</v>
+        <v>4.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13790</v>
+        <v>4430</v>
       </c>
       <c r="K9" t="n">
-        <v>13410</v>
+        <v>4650</v>
       </c>
       <c r="L9" t="n">
-        <v>14140</v>
+        <v>4855</v>
       </c>
       <c r="M9" t="n">
-        <v>11600</v>
+        <v>4185</v>
       </c>
       <c r="N9" t="n">
-        <v>0.24</v>
+        <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>49674018535</v>
+        <v>85658477924</v>
       </c>
       <c r="P9" t="n">
-        <v>28700</v>
+        <v>5470</v>
       </c>
       <c r="Q9" t="n">
-        <v>11600</v>
+        <v>2810</v>
       </c>
       <c r="R9" t="n">
-        <v>17000</v>
+        <v>-469000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>덕산넵코어스의 사기 상장 및 중복 상장 의혹 제기, 금감원 신고 및 국민권익위 조사 요청.</t>
+          <t>미국 항생제 보유 회사 주가 폭등 속보와 WHO의 러시아 폐렴 관련 상황 파악 미흡 소식에 따른 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['중복 상장', '사기 상장', '공매도']</t>
+          <t>['항생제', '폐렴', 'WHO']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1724000</v>
+        <v>45850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'-0.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>266</v>
       </c>
       <c r="F10" t="n">
-        <v>426</v>
+        <v>154</v>
       </c>
       <c r="G10" t="n">
-        <v>1416</v>
+        <v>1011</v>
       </c>
       <c r="H10" t="n">
-        <v>49.59</v>
+        <v>13.39</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1723000</v>
+        <v>45900</v>
       </c>
       <c r="K10" t="n">
-        <v>1722000</v>
+        <v>45950</v>
       </c>
       <c r="L10" t="n">
-        <v>1759000</v>
+        <v>46500</v>
       </c>
       <c r="M10" t="n">
-        <v>1722000</v>
+        <v>45100</v>
       </c>
       <c r="N10" t="n">
-        <v>49.71</v>
+        <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>2466388892000</v>
+        <v>28497404825</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>403000</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-25000</v>
+        <v>-12000</v>
       </c>
       <c r="S10" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>솔리다임 상장 이슈와 관련된 논란 및 주주 통수 의혹, 정부 정책에 대한 불만과 주가 하락에 대한 부정적 전망.</t>
+          <t>리보세라닙 병용요법 허가 기대감. 공매도 발악 및 무상증자 가능성 언급. 우상향 차트 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '자사주']</t>
+          <t>['리보세라닙', '공매도', '무상증자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45900</v>
+        <v>8210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>263</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>971</v>
+        <v>210</v>
       </c>
       <c r="H11" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K11" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L11" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M11" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N11" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O11" t="n">
-        <v>28106934675</v>
+        <v>13155189515</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R11" t="n">
-        <v>-12000</v>
+        <v>-6000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 기대감과 공매도 세력 발악 언급, 2026년 연말 30만 목표 및 우상향 차트 시작 주장.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '허가']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8240</v>
+        <v>1710500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>434</v>
       </c>
       <c r="G12" t="n">
-        <v>208</v>
+        <v>1421</v>
       </c>
       <c r="H12" t="n">
-        <v>26.38</v>
+        <v>49.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8250</v>
+        <v>1723000</v>
       </c>
       <c r="K12" t="n">
-        <v>8190</v>
+        <v>1722000</v>
       </c>
       <c r="L12" t="n">
-        <v>8320</v>
+        <v>1759000</v>
       </c>
       <c r="M12" t="n">
-        <v>8090</v>
+        <v>1707000</v>
       </c>
       <c r="N12" t="n">
-        <v>26.55</v>
+        <v>49.71</v>
       </c>
       <c r="O12" t="n">
-        <v>12773256955</v>
+        <v>2650204641000</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>8090</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>-6000</v>
+        <v>-25000</v>
       </c>
       <c r="S12" t="n">
-        <v>44000</v>
+        <v>-2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>솔리다임 상장 관련 논란, 주주 이익 침해 의혹. 외인 매도세 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['솔리다임', '주주 이익', '외인 매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>266250</v>
+        <v>264750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G13" t="n">
-        <v>1736</v>
+        <v>1790</v>
       </c>
       <c r="H13" t="n">
         <v>46.38</v>
@@ -1616,13 +1616,13 @@
         <v>270000</v>
       </c>
       <c r="M13" t="n">
-        <v>265000</v>
+        <v>264500</v>
       </c>
       <c r="N13" t="n">
         <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>2519079486000</v>
+        <v>2644351496000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자 107조 영업이익에도 주가 부양이 되지 않는 현실에 대한 불만과 실적 대비 주가 부양 실패 지적.</t>
+          <t>영업이익 107조에도 주가 부양 실패, 국장 현실 비판. 외인 매수세 의문 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '실적']</t>
+          <t>['영업이익', '주가 부양', '국장 현실']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16850</v>
+        <v>16810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.83%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F14" t="n">
         <v>54</v>
       </c>
       <c r="G14" t="n">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="H14" t="n">
         <v>9.460000000000001</v>
@@ -1714,7 +1714,7 @@
         <v>9.5</v>
       </c>
       <c r="O14" t="n">
-        <v>30891753595</v>
+        <v>31324421265</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 및 주가 조작 의혹 제기, 기관 투자자에 대한 불신과 주주 호소문 반복 게시.</t>
+          <t>주가 조작 의혹 제기, 공매도 과열 종목 지정 요구. 연기금 및 삼성자산운용 참여 의문.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '주가 조작', '주주 호소']</t>
+          <t>['주가 조작', '공매도', '연기금']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,18 +1763,18 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18980</v>
+        <v>18930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
         <v>62</v>
@@ -1806,7 +1806,7 @@
         <v>27.67</v>
       </c>
       <c r="O15" t="n">
-        <v>34592863200</v>
+        <v>35501026120</v>
       </c>
       <c r="P15" t="n">
         <v>35350</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>증권사 애널리스트 및 리딩방 정보에 대한 불신과 조선주 전반의 실적 부진 및 주가 하락에 대한 우려.</t>
+          <t>증권사 애널리스트 불신, 조선주 폭락 원인 규명 요구. 실적 발표 및 수주 관련 의구심.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '수주']</t>
+          <t>['조선주', '실적 발표', '수주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,79 +1851,79 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28400</v>
+        <v>230500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.76</v>
+        <v>-0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G16" t="n">
-        <v>160</v>
+        <v>698</v>
       </c>
       <c r="H16" t="n">
-        <v>10.02</v>
+        <v>3.47</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>29800</v>
+        <v>241000</v>
       </c>
       <c r="K16" t="n">
-        <v>29900</v>
+        <v>227000</v>
       </c>
       <c r="L16" t="n">
-        <v>30000</v>
+        <v>239500</v>
       </c>
       <c r="M16" t="n">
-        <v>28250</v>
+        <v>210500</v>
       </c>
       <c r="N16" t="n">
-        <v>10.78</v>
+        <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>51042004100</v>
+        <v>38301540250</v>
       </c>
       <c r="P16" t="n">
-        <v>75900</v>
+        <v>1233000</v>
       </c>
       <c r="Q16" t="n">
-        <v>15960</v>
+        <v>120000</v>
       </c>
       <c r="R16" t="n">
-        <v>-380000</v>
+        <v>5000</v>
       </c>
       <c r="S16" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>공매도 금지 조치 및 릴레이 계약 공시 가능성에 따른 기대감. 연기금의 7일 연속 매수세 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['공매도 금지', '계약 공시', '연기금']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,91 +1931,91 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>229500</v>
+        <v>28350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.65</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>678</v>
+        <v>162</v>
       </c>
       <c r="H17" t="n">
-        <v>3.47</v>
+        <v>10.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>241000</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
-        <v>227000</v>
+        <v>29900</v>
       </c>
       <c r="L17" t="n">
-        <v>239500</v>
+        <v>30000</v>
       </c>
       <c r="M17" t="n">
-        <v>210500</v>
+        <v>28250</v>
       </c>
       <c r="N17" t="n">
-        <v>4.12</v>
+        <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>37810128250</v>
+        <v>51561170975</v>
       </c>
       <c r="P17" t="n">
-        <v>1233000</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>120000</v>
+        <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>5000</v>
+        <v>-380000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 금지 조치 및 릴레이 계약 공시 가능성에 따른 기대감. 연기금의 7일 연속 매수세 확인.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도 금지', '계약 공시', '연기금']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17020</v>
+        <v>16900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.13%</t>
+          <t>'-5.80%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F18" t="n">
         <v>70</v>
       </c>
       <c r="G18" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>81953599900</v>
+        <v>83295491795</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2091,10 +2091,10 @@
         <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-168000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7380</v>
+        <v>7350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.63%</t>
+          <t>'-6.01%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.03</v>
       </c>
       <c r="E19" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="H19" t="n">
         <v>3.09</v>
@@ -2174,7 +2174,7 @@
         <v>5.12</v>
       </c>
       <c r="O19" t="n">
-        <v>80608538435</v>
+        <v>81043641580</v>
       </c>
       <c r="P19" t="n">
         <v>23500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>삼표시멘트의 부동산 개발 관련 기대감과 PF 대주단 구성 소식에도 불구하고 주가 하락.</t>
+          <t>본PF 대주단 구성 진행, 부동산주 연계 분석. 주포 운전 및 물량 간수 의혹.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['부동산 개발', 'PF', '시멘트']</t>
+          <t>['본PF', '부동산주', '주포']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75700</v>
+        <v>75500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.96%</t>
+          <t>'-6.21%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="F20" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G20" t="n">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="H20" t="n">
         <v>22.49</v>
@@ -2266,7 +2266,7 @@
         <v>22.59</v>
       </c>
       <c r="O20" t="n">
-        <v>172943749100</v>
+        <v>176402076300</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 텍사스 가스 발전 확정 및 한국 관세 인하 가능성에도 불구하고 원전 관련 부정적 전망과 하락세에 대한 실망감.</t>
+          <t>텍사스 가스 발전 확정에도 주가 하락 지속. 원전 사업 전망 불투명, 공매도 비판.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['가스 발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4855</v>
+        <v>4825</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-7.39%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2332,7 +2332,7 @@
         <v>58</v>
       </c>
       <c r="G21" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="H21" t="n">
         <v>4.65</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>62732296378</v>
+        <v>63338907834</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53800</v>
+        <v>53700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.40%</t>
+          <t>'-7.57%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>287</v>
       </c>
       <c r="F22" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G22" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2444,13 +2444,13 @@
         <v>63800</v>
       </c>
       <c r="M22" t="n">
-        <v>53100</v>
+        <v>53000</v>
       </c>
       <c r="N22" t="n">
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>50808442900</v>
+        <v>51230529550</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>국내 시장 석권 준비 및 미국 비만주 급등 소식에도 불구하고 이해할 수 없는 급락과 주가 조작 의혹 제기.</t>
+          <t>미국 비만주 급등과 비교, 기술 수출 반환 의혹. 주가 조작 및 차명거래 의심, 금감원 신고.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비만주', '주가조작', '급락']</t>
+          <t>['비만주', '기술 수출', '주가 조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15240</v>
+        <v>15080</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.80%</t>
+          <t>'-9.75%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H23" t="n">
         <v>0.93</v>
@@ -2542,7 +2542,7 @@
         <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>32483225680</v>
+        <v>32801534115</v>
       </c>
       <c r="P23" t="n">
         <v>17590</v>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9900</v>
+        <v>9870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.08%</t>
+          <t>'-10.35%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>61</v>
       </c>
       <c r="G24" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>6647050960</v>
+        <v>6717355815</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_12.xlsx
+++ b/data/trending_integrated_20261008_12.xlsx
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30924146480</v>
+        <v>30980494780</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13950</v>
+        <v>11390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.35%</t>
+          <t>'+15.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="H3" t="n">
-        <v>4.43</v>
+        <v>37.45</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11990</v>
+        <v>9880</v>
       </c>
       <c r="K3" t="n">
-        <v>14330</v>
+        <v>10030</v>
       </c>
       <c r="L3" t="n">
-        <v>14980</v>
+        <v>11540</v>
       </c>
       <c r="M3" t="n">
-        <v>13070</v>
+        <v>9850</v>
       </c>
       <c r="N3" t="n">
-        <v>4.66</v>
+        <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>42088796855</v>
+        <v>56660437190</v>
       </c>
       <c r="P3" t="n">
-        <v>14980</v>
+        <v>19150</v>
       </c>
       <c r="Q3" t="n">
-        <v>6500</v>
+        <v>3445</v>
       </c>
       <c r="R3" t="n">
-        <v>48000</v>
+        <v>219000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>191000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼성전기향 차세대 유리기판 핵심 부품 공급 계약 및 공동 개발 뉴스 기반 강세. 매출 및 영업이익 증가 전망.</t>
+          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스본더', '공급']</t>
+          <t>['전구체', '양극재', '매출']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11400</v>
+        <v>13710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.38%</t>
+          <t>'+14.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>195</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
-        <v>37.45</v>
+        <v>4.43</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9880</v>
+        <v>11990</v>
       </c>
       <c r="K4" t="n">
-        <v>10030</v>
+        <v>14330</v>
       </c>
       <c r="L4" t="n">
-        <v>11540</v>
+        <v>14980</v>
       </c>
       <c r="M4" t="n">
-        <v>9850</v>
+        <v>13070</v>
       </c>
       <c r="N4" t="n">
-        <v>37.41</v>
+        <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>55870000645</v>
+        <v>42685901305</v>
       </c>
       <c r="P4" t="n">
-        <v>19150</v>
+        <v>14980</v>
       </c>
       <c r="Q4" t="n">
-        <v>3445</v>
+        <v>6500</v>
       </c>
       <c r="R4" t="n">
-        <v>219000</v>
+        <v>48000</v>
       </c>
       <c r="S4" t="n">
-        <v>191000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
+          <t>삼성전기향 차세대 유리기판 핵심 부품 공급 계약 및 공동 개발 뉴스 기반 강세. 매출 및 영업이익 증가 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전구체', '양극재', '매출']</t>
+          <t>['유리기판', '글라스본더', '공급']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6850</v>
+        <v>14880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.04%</t>
+          <t>'+7.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>371</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="G5" t="n">
-        <v>184</v>
+        <v>1045</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6460</v>
+        <v>13790</v>
       </c>
       <c r="K5" t="n">
-        <v>6930</v>
+        <v>13410</v>
       </c>
       <c r="L5" t="n">
-        <v>8390</v>
+        <v>14880</v>
       </c>
       <c r="M5" t="n">
-        <v>6730</v>
+        <v>11600</v>
       </c>
       <c r="N5" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="O5" t="n">
-        <v>20200395015</v>
+        <v>79635861205</v>
       </c>
       <c r="P5" t="n">
-        <v>9680</v>
+        <v>28700</v>
       </c>
       <c r="Q5" t="n">
-        <v>371</v>
+        <v>11600</v>
       </c>
       <c r="R5" t="n">
-        <v>-25000</v>
+        <v>17000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 중견소속부 변경이라는 호재가 언급되었으나, 기대감만 있고 구체적인 근거 제시 부족. 주가 급등 후 조정 양상.</t>
+          <t>사기 상장 의혹 제기 및 정부의 무능함 비판. 주가 하락에 대한 강한 불만.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['관리종목 해제', '호재', '주가']</t>
+          <t>['사기 상장', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14620</v>
+        <v>38300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.02%</t>
+          <t>'+5.80%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>334</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>964</v>
+        <v>189</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09</v>
+        <v>31.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13790</v>
+        <v>36200</v>
       </c>
       <c r="K6" t="n">
-        <v>13410</v>
+        <v>36250</v>
       </c>
       <c r="L6" t="n">
-        <v>14680</v>
+        <v>39850</v>
       </c>
       <c r="M6" t="n">
-        <v>11600</v>
+        <v>36000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.24</v>
+        <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>65984389060</v>
+        <v>112322025475</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>45000</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>15530</v>
       </c>
       <c r="R6" t="n">
-        <v>17000</v>
+        <v>199000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중복 상장 및 무차별 공매도 관련 금융당국 조사 요청. 주가 조작 및 사기 상장 의혹 제기.</t>
+          <t>JP모건 등 기관 및 외국인 매수세 유입과 추세적 상승에 대한 긍정적 전망, 하락장에서도 주가 버텨준 점 강조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['중복 상장', '공매도', '금융당국']</t>
+          <t>['기관매수', '추세', '외국인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38300</v>
+        <v>6810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.80%</t>
+          <t>'+5.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H7" t="n">
-        <v>31.86</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36200</v>
+        <v>6460</v>
       </c>
       <c r="K7" t="n">
-        <v>36250</v>
+        <v>6930</v>
       </c>
       <c r="L7" t="n">
-        <v>39850</v>
+        <v>8390</v>
       </c>
       <c r="M7" t="n">
-        <v>36000</v>
+        <v>6730</v>
       </c>
       <c r="N7" t="n">
-        <v>31.78</v>
+        <v>0.31</v>
       </c>
       <c r="O7" t="n">
-        <v>111305423850</v>
+        <v>20373084485</v>
       </c>
       <c r="P7" t="n">
-        <v>45000</v>
+        <v>9680</v>
       </c>
       <c r="Q7" t="n">
-        <v>15530</v>
+        <v>371</v>
       </c>
       <c r="R7" t="n">
-        <v>199000</v>
+        <v>-25000</v>
       </c>
       <c r="S7" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>JP모건 등 기관 및 외국인 매수세 유입과 추세적 상승에 대한 긍정적 전망, 하락장에서도 주가 버텨준 점 강조.</t>
+          <t>관리종목 해제 및 중견소속부 변경 호재에 대한 기대감 있으나, 주포 등장 및 거래량 부재, 매물대 걸림 등 불확실성 상존.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관매수', '추세', '외국인']</t>
+          <t>['관리종목', '호재', '거래량']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13160</v>
+        <v>13130</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.69%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H8" t="n">
         <v>1.07</v>
@@ -1162,7 +1162,7 @@
         <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>80515960620</v>
+        <v>81455618535</v>
       </c>
       <c r="P8" t="n">
         <v>22250</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유증 물량 정리 완료 후 상승 기대. 바이오스텝 관련 기대감, 1차 목표가 3만원 제시.</t>
+          <t>유증 물량 정리 및 바이오스텝 관련 기대감. 1차 목표가 3만원 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유증 물량', '바이오스텝', '목표가']</t>
+          <t>['유증', '바이오스텝']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4465</v>
+        <v>4430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.79%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1.19</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H9" t="n">
         <v>4.46</v>
@@ -1254,7 +1254,7 @@
         <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>85658477924</v>
+        <v>86118830289</v>
       </c>
       <c r="P9" t="n">
         <v>5470</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등 속보와 WHO의 러시아 폐렴 관련 상황 파악 미흡 소식에 따른 기대감.</t>
+          <t>전염병 관련 이슈로 인한 기대감 형성. WHO의 상황 파악 지연 및 확산세 둔화 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', 'WHO']</t>
+          <t>['전염병', 'WHO']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45850</v>
+        <v>45750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'-0.33%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F10" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G10" t="n">
-        <v>1011</v>
+        <v>1050</v>
       </c>
       <c r="H10" t="n">
         <v>13.39</v>
@@ -1346,7 +1346,7 @@
         <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>28497404825</v>
+        <v>28915275800</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 기대감. 공매도 발악 및 무상증자 가능성 언급. 우상향 차트 분석.</t>
+          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 2026년 연말 30만 목표 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '무상증자']</t>
+          <t>['리보세라닙', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8210</v>
+        <v>8180</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
         <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="H11" t="n">
         <v>26.38</v>
@@ -1438,7 +1438,7 @@
         <v>26.55</v>
       </c>
       <c r="O11" t="n">
-        <v>13155189515</v>
+        <v>13707056025</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1710500</v>
+        <v>1700000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-1.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>434</v>
       </c>
       <c r="G12" t="n">
-        <v>1421</v>
+        <v>1355</v>
       </c>
       <c r="H12" t="n">
         <v>49.59</v>
@@ -1524,13 +1524,13 @@
         <v>1759000</v>
       </c>
       <c r="M12" t="n">
-        <v>1707000</v>
+        <v>1699000</v>
       </c>
       <c r="N12" t="n">
         <v>49.71</v>
       </c>
       <c r="O12" t="n">
-        <v>2650204641000</v>
+        <v>2793356330500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 논란, 주주 이익 침해 의혹. 외인 매도세 및 정부 정책 비판.</t>
+          <t>정치적 이슈와 연계된 주가 하락 논의. 솔리다임 상장 관련 논란.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['솔리다임', '주주 이익', '외인 매도']</t>
+          <t>['솔리다임', '주가 조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>264750</v>
+        <v>264250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.40%</t>
+          <t>'-1.58%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G13" t="n">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="H13" t="n">
         <v>46.38</v>
@@ -1616,13 +1616,13 @@
         <v>270000</v>
       </c>
       <c r="M13" t="n">
-        <v>264500</v>
+        <v>263500</v>
       </c>
       <c r="N13" t="n">
         <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>2644351496000</v>
+        <v>2800642932750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>영업이익 107조에도 주가 부양 실패, 국장 현실 비판. 외인 매수세 의문 제기.</t>
+          <t>높은 영업이익에도 불구하고 주가 부양 실패. 시장 및 정치적 요인에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '국장 현실']</t>
+          <t>['영업이익', '주가 부양']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16810</v>
+        <v>18930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F14" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="H14" t="n">
-        <v>9.460000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17340</v>
+        <v>19540</v>
       </c>
       <c r="K14" t="n">
-        <v>17190</v>
+        <v>19490</v>
       </c>
       <c r="L14" t="n">
-        <v>17220</v>
+        <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>16710</v>
+        <v>18910</v>
       </c>
       <c r="N14" t="n">
-        <v>9.5</v>
+        <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>31324421265</v>
+        <v>35961124975</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>70000</v>
+        <v>-255000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-24000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기, 공매도 과열 종목 지정 요구. 연기금 및 삼성자산운용 참여 의문.</t>
+          <t>증권사 애널리스트 불신, 조선주 폭락 원인 규명 요구. 실적 발표 및 수주 관련 의구심.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '연기금']</t>
+          <t>['조선주', '실적 발표', '수주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18930</v>
+        <v>16770</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>329</v>
+        <v>463</v>
       </c>
       <c r="H15" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19540</v>
+        <v>17340</v>
       </c>
       <c r="K15" t="n">
-        <v>19490</v>
+        <v>17190</v>
       </c>
       <c r="L15" t="n">
-        <v>19500</v>
+        <v>17220</v>
       </c>
       <c r="M15" t="n">
-        <v>18910</v>
+        <v>16710</v>
       </c>
       <c r="N15" t="n">
-        <v>27.67</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>35501026120</v>
+        <v>33194014835</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>18440</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-255000</v>
+        <v>70000</v>
       </c>
       <c r="S15" t="n">
-        <v>-24000</v>
+        <v>-1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>증권사 애널리스트 불신, 조선주 폭락 원인 규명 요구. 실적 발표 및 수주 관련 의구심.</t>
+          <t>공매도 관련 게시글 다수. 주주들에게 대차 해지 중요성 호소.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['조선주', '실적 발표', '수주']</t>
+          <t>['공매도', '대차 해지']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,86 +1844,86 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>230500</v>
+        <v>28300</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.36%</t>
+          <t>'-5.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.65</v>
+        <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>698</v>
+        <v>160</v>
       </c>
       <c r="H16" t="n">
-        <v>3.47</v>
+        <v>10.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>241000</v>
+        <v>29800</v>
       </c>
       <c r="K16" t="n">
-        <v>227000</v>
+        <v>29900</v>
       </c>
       <c r="L16" t="n">
-        <v>239500</v>
+        <v>30000</v>
       </c>
       <c r="M16" t="n">
-        <v>210500</v>
+        <v>28250</v>
       </c>
       <c r="N16" t="n">
-        <v>4.12</v>
+        <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>38301540250</v>
+        <v>53226004525</v>
       </c>
       <c r="P16" t="n">
-        <v>1233000</v>
+        <v>75900</v>
       </c>
       <c r="Q16" t="n">
-        <v>120000</v>
+        <v>15960</v>
       </c>
       <c r="R16" t="n">
-        <v>5000</v>
+        <v>-380000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 금지 조치 및 릴레이 계약 공시 가능성에 따른 기대감. 연기금의 7일 연속 매수세 확인.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도 금지', '계약 공시', '연기금']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,91 +1931,91 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28350</v>
+        <v>228500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-5.19%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>-0.65</v>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>162</v>
+        <v>720</v>
       </c>
       <c r="H17" t="n">
-        <v>10.02</v>
+        <v>3.47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>241000</v>
       </c>
       <c r="K17" t="n">
-        <v>29900</v>
+        <v>227000</v>
       </c>
       <c r="L17" t="n">
-        <v>30000</v>
+        <v>239500</v>
       </c>
       <c r="M17" t="n">
-        <v>28250</v>
+        <v>210500</v>
       </c>
       <c r="N17" t="n">
-        <v>10.78</v>
+        <v>4.12</v>
       </c>
       <c r="O17" t="n">
-        <v>51561170975</v>
+        <v>38933159750</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>1233000</v>
       </c>
       <c r="Q17" t="n">
-        <v>15960</v>
+        <v>120000</v>
       </c>
       <c r="R17" t="n">
-        <v>-380000</v>
+        <v>5000</v>
       </c>
       <c r="S17" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>공매도 금지 조치 및 릴레이 계약 공시 가능성에 따른 기대감. 연기금의 7일 연속 매수세 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['공매도 금지', '계약 공시', '연기금']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16900</v>
+        <v>16820</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.80%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" t="n">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>83295491795</v>
+        <v>85500806265</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7350</v>
+        <v>75400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.01%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-2.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>171</v>
+        <v>387</v>
       </c>
       <c r="F19" t="n">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="G19" t="n">
-        <v>476</v>
+        <v>1087</v>
       </c>
       <c r="H19" t="n">
-        <v>3.09</v>
+        <v>22.49</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7820</v>
+        <v>80500</v>
       </c>
       <c r="K19" t="n">
-        <v>8080</v>
+        <v>79600</v>
       </c>
       <c r="L19" t="n">
-        <v>8510</v>
+        <v>79600</v>
       </c>
       <c r="M19" t="n">
-        <v>7170</v>
+        <v>75300</v>
       </c>
       <c r="N19" t="n">
-        <v>5.12</v>
+        <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>81043641580</v>
+        <v>179257440000</v>
       </c>
       <c r="P19" t="n">
-        <v>23500</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>2890</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-501000</v>
+        <v>-360000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-54000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>본PF 대주단 구성 진행, 부동산주 연계 분석. 주포 운전 및 물량 간수 의혹.</t>
+          <t>해외 가스 발전 수주 확정 소식에도 불구하고 주가 하락 지속. 공매도 및 시장 상황에 대한 불만.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['본PF', '부동산주', '주포']</t>
+          <t>['가스 발전', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,86 +2212,86 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75500</v>
+        <v>7310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.21%</t>
+          <t>'-6.52%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>379</v>
+        <v>171</v>
       </c>
       <c r="F20" t="n">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>1032</v>
+        <v>491</v>
       </c>
       <c r="H20" t="n">
-        <v>22.49</v>
+        <v>3.09</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>80500</v>
+        <v>7820</v>
       </c>
       <c r="K20" t="n">
-        <v>79600</v>
+        <v>8080</v>
       </c>
       <c r="L20" t="n">
-        <v>79600</v>
+        <v>8510</v>
       </c>
       <c r="M20" t="n">
-        <v>75300</v>
+        <v>7170</v>
       </c>
       <c r="N20" t="n">
-        <v>22.59</v>
+        <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>176402076300</v>
+        <v>81308866770</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>23500</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>2890</v>
       </c>
       <c r="R20" t="n">
-        <v>-360000</v>
+        <v>-501000</v>
       </c>
       <c r="S20" t="n">
-        <v>-54000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>텍사스 가스 발전 확정에도 주가 하락 지속. 원전 사업 전망 불투명, 공매도 비판.</t>
+          <t>본PF 진행 및 대주단 구성 중. 부동산 시장 및 시멘트 업황에 대한 전망 엇갈림.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['가스 발전', '원전', '공매도']</t>
+          <t>['본PF', '부동산']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4825</v>
+        <v>4805</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.39%</t>
+          <t>'-7.77%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H21" t="n">
         <v>4.65</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>63338907834</v>
+        <v>64136621876</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53700</v>
+        <v>53500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.57%</t>
+          <t>'-7.92%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F22" t="n">
         <v>145</v>
       </c>
       <c r="G22" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2450,7 +2450,7 @@
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>51230529550</v>
+        <v>51452932150</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 비만주 급등과 비교, 기술 수출 반환 의혹. 주가 조작 및 차명거래 의심, 금감원 신고.</t>
+          <t>미국 비만주 급등과 대비되는 국내 주가 하락. 주가 조작 및 공매도 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비만주', '기술 수출', '주가 조작']</t>
+          <t>['비만 치료제', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15080</v>
+        <v>15030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.75%</t>
+          <t>'-10.05%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H23" t="n">
         <v>0.93</v>
@@ -2542,7 +2542,7 @@
         <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>32801534115</v>
+        <v>33160148840</v>
       </c>
       <c r="P23" t="n">
         <v>17590</v>
@@ -2591,21 +2591,21 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9870</v>
+        <v>9880</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.35%</t>
+          <t>'-10.26%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G24" t="n">
         <v>343</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>6717355815</v>
+        <v>6798637560</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>
